--- a/results/phase/yield_class/model_results_yield_class.xlsx
+++ b/results/phase/yield_class/model_results_yield_class.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,41 +425,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>feature_set</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>threshold_median</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>f1_score</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
@@ -456,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>NDRE_phase3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForestClassifier</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0.23476</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="G2" t="n">
         <v>0.8</v>
@@ -483,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>phase4_indices</t>
+          <t>CI_phase3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -495,13 +507,13 @@
         <v>0.23476</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="E3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.7272727272727273</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.6666666666666666</v>
       </c>
       <c r="G3" t="n">
         <v>0.8</v>
@@ -510,7 +522,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N_test_only</t>
+          <t>combined</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -522,13 +534,13 @@
         <v>0.23476</v>
       </c>
       <c r="D4" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="G4" t="n">
         <v>0.8</v>
@@ -537,34 +549,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>all_phases_indices</t>
+          <t>phase4_indices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForestClassifier</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0.23476</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>phase4_indices</t>
+          <t>NDRE_only</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,130 +588,130 @@
         <v>0.23476</v>
       </c>
       <c r="D6" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.75</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>all_phases_indices</t>
+          <t>CI_only</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RandomForestClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>0.23476</v>
       </c>
       <c r="D7" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.75</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>N_test_only</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RandomForestClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0.23476</v>
       </c>
       <c r="D8" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>phase2_indices</t>
+          <t>N_test_phase1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RandomForestClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0.23476</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>phase3_indices</t>
+          <t>N_test_phase2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RandomForestClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0.23476</v>
       </c>
       <c r="D10" t="n">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>phase1_indices</t>
+          <t>N_test_phase3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -711,123 +723,1635 @@
         <v>0.23476</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="F11" t="n">
-        <v>0.375</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>phase1_indices</t>
+          <t>N_test_phase4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RandomForestClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0.23476</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="F12" t="n">
-        <v>0.375</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>phase2_indices</t>
+          <t>NDVI_phase4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForestClassifier</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>0.23476</v>
       </c>
       <c r="D13" t="n">
-        <v>0.35</v>
+        <v>0.65</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N_test_only</t>
+          <t>phase2_combined</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RandomForestClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>0.23476</v>
       </c>
       <c r="D14" t="n">
-        <v>0.25</v>
+        <v>0.65</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>phase4_combined</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>phase4_combined</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>all_phases_indices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NDVI_only</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>phase2_combined</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NDVI_only</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CI_phase4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GNDVI_only</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NDRE_phase4</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CI_phase4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>phase3_combined</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>phase3_combined</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NDRE_phase2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NDRE_phase4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CI_phase2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>phase4_indices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>all_phases_indices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NDVI_phase1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NDRE_phase1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CI_phase1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GNDVI_phase3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NDRE_only</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CI_only</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>phase1_combined</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NDVI_phase4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>phase2_indices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GNDVI_phase1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NDVI_phase1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NDVI_phase3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GNDVI_only</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>phase3_indices</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.23476</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>phase1_combined</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>GNDVI_phase1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GNDVI_phase4</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>GNDVI_phase2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NDRE_phase1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CI_phase1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NDRE_phase3</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CI_phase3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>phase1_indices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>phase1_indices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NDVI_phase2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>GNDVI_phase4</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>phase2_indices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NDVI_phase2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NDRE_phase2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CI_phase2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>NDVI_phase3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="F63" t="n">
         <v>0.25</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G63" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>GNDVI_phase2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>GNDVI_phase3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>N_test_only</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E66" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F66" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G66" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>N_test_phase1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>N_test_phase2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>N_test_phase3</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>N_test_phase4</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>phase3_indices</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="G71" t="n">
         <v>0.3</v>
       </c>
     </row>
